--- a/output/2026-09-25/enriched_analysis.xlsx
+++ b/output/2026-09-25/enriched_analysis.xlsx
@@ -3669,25 +3669,25 @@
         <v>625.85</v>
       </c>
       <c r="J14" t="n">
-        <v>630.67</v>
+        <v>632.66</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="L14" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="N14" t="n">
-        <v>46955184</v>
+        <v>44358875</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>46955184</v>
+        <v>44358875</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.407</v>
+        <v>0.384</v>
       </c>
       <c r="W14" t="n">
         <v>1155</v>
@@ -3751,10 +3751,10 @@
         <v>39.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>630.668797765033</v>
+        <v>632.6588461812736</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>23-06-2026</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="AQ14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR14" t="n">
         <v>94</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>98</v>
       </c>
       <c r="AS14" t="n">
         <v>4</v>
@@ -5021,12 +5021,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5038,40 +5038,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
         <v>-1</v>
       </c>
       <c r="I20" t="n">
-        <v>177.35</v>
+        <v>216.79</v>
       </c>
       <c r="J20" t="n">
-        <v>169.88</v>
+        <v>210</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="L20" t="n">
-        <v>61.48</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="N20" t="n">
-        <v>5988193</v>
+        <v>5944992</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5988193</v>
+        <v>5944992</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5085,124 +5085,124 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.285</v>
+        <v>0.293</v>
       </c>
       <c r="W20" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="X20" t="n">
-        <v>36.4</v>
+        <v>25.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>-44</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>-3.28</v>
+        <v>0.03</v>
       </c>
       <c r="AA20" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.25</v>
+        <v>7.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.44</v>
+        <v>-0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>-35.96</v>
+        <v>3.16</v>
       </c>
       <c r="AG20" t="n">
-        <v>175.12</v>
+        <v>209.69</v>
       </c>
       <c r="AH20" t="n">
-        <v>179.25</v>
+        <v>196.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>24.8</v>
+        <v>19.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>169.8778156028369</v>
+        <v>210.0036030944223</v>
       </c>
       <c r="AK20" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="AS20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>2000469</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5988193</v>
+        <v>1710211</v>
       </c>
       <c r="BA20" t="n">
-        <v>5988193</v>
+        <v>3296491</v>
       </c>
       <c r="BB20" t="n">
-        <v>5988193</v>
+        <v>5944992</v>
       </c>
       <c r="BC20" t="n">
-        <v>5988193</v>
+        <v>5944992</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5235,10 +5235,10 @@
         <v>0</v>
       </c>
       <c r="BN20" t="n">
-        <v>2000469</v>
+        <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>5988193</v>
+        <v>3296491</v>
       </c>
       <c r="BP20" t="n">
         <v>1</v>
@@ -5247,18 +5247,18 @@
         <v>0</v>
       </c>
       <c r="BR20" t="n">
-        <v>0.3341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5270,171 +5270,171 @@
         </is>
       </c>
       <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>177.35</v>
+      </c>
+      <c r="J21" t="n">
+        <v>169.88</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>61.48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5988193</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5988193</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="W21" t="n">
+        <v>210</v>
+      </c>
+      <c r="X21" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>141</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-4.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AE21" t="b">
         <v>1</v>
       </c>
-      <c r="F21" t="n">
-        <v>18</v>
-      </c>
-      <c r="G21" t="n">
-        <v>17</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>336</v>
-      </c>
-      <c r="J21" t="n">
-        <v>335.41</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4081958</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4081958</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S21" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="AF21" t="n">
+        <v>-35.96</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>175.12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>169.8778156028369</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS21" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5507</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9.31</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>223</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>175</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.97</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>365.15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>335.45</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>335.4115036976171</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ21" t="n">
-        <v>49</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>87</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>38</v>
-      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>2000469</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>5988193</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>5988193</v>
       </c>
       <c r="BB21" t="n">
-        <v>1094828</v>
+        <v>5988193</v>
       </c>
       <c r="BC21" t="n">
-        <v>4081958</v>
+        <v>5988193</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5467,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>0</v>
+        <v>2000469</v>
       </c>
       <c r="BO21" t="n">
-        <v>0</v>
+        <v>5988193</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5479,18 +5479,18 @@
         <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>0</v>
+        <v>0.3341</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5502,171 +5502,171 @@
         </is>
       </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>336</v>
+      </c>
+      <c r="J22" t="n">
+        <v>335.41</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4081958</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4081958</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5507</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>223</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>175</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>21</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>216.79</v>
-      </c>
-      <c r="J22" t="n">
-        <v>210</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S22" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>12</v>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="W22" t="n">
-        <v>203</v>
-      </c>
-      <c r="X22" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>3.16</v>
-      </c>
       <c r="AG22" t="n">
-        <v>209.69</v>
+        <v>365.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>196.32</v>
+        <v>335.45</v>
       </c>
       <c r="AI22" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>210.0036030944223</v>
+        <v>335.4115036976171</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
           <t>18-08-2026</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
       <c r="AQ22" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="AR22" t="n">
+        <v>87</v>
+      </c>
+      <c r="AS22" t="n">
         <v>38</v>
       </c>
-      <c r="AS22" t="n">
-        <v>8</v>
-      </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1710211</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3296491</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>5944992</v>
+        <v>1094828</v>
       </c>
       <c r="BC22" t="n">
-        <v>5944992</v>
+        <v>4081958</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="BO22" t="n">
-        <v>3296491</v>
+        <v>0</v>
       </c>
       <c r="BP22" t="n">
         <v>1</v>
@@ -5717,12 +5717,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5734,40 +5734,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>201.63</v>
+        <v>230.91</v>
       </c>
       <c r="J23" t="n">
-        <v>191.87</v>
+        <v>234.4</v>
       </c>
       <c r="K23" t="n">
-        <v>5.1</v>
+        <v>-1.5</v>
       </c>
       <c r="L23" t="n">
-        <v>70.02</v>
+        <v>67.13</v>
       </c>
       <c r="M23" t="n">
-        <v>1.34</v>
+        <v>0.3</v>
       </c>
       <c r="N23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -5785,96 +5785,96 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.038</v>
+        <v>0.043</v>
       </c>
       <c r="W23" t="n">
-        <v>3539</v>
+        <v>693</v>
       </c>
       <c r="X23" t="n">
-        <v>21</v>
+        <v>11.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Z23" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="AA23" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>6.54</v>
       </c>
       <c r="AC23" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>207.06</v>
+        <v>227.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>193.72</v>
+        <v>205</v>
       </c>
       <c r="AI23" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>191.8684857142857</v>
+        <v>234.4008293560754</v>
       </c>
       <c r="AK23" t="n">
-        <v>5.1</v>
+        <v>-1.5</v>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ23" t="n">
         <v>2</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AS23" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
         <v>3</v>
@@ -5886,19 +5886,19 @@
         <v>3</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BA23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="BB23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="BC23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
@@ -5931,30 +5931,30 @@
         <v>0</v>
       </c>
       <c r="BN23" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BO23" t="n">
-        <v>13430794</v>
+        <v>2995877</v>
       </c>
       <c r="BP23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ23" t="n">
         <v>0</v>
       </c>
       <c r="BR23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5966,40 +5966,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>646.6</v>
+        <v>249.6</v>
       </c>
       <c r="J24" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="K24" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="L24" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6017,118 +6017,120 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.024</v>
+        <v>0.165</v>
       </c>
       <c r="W24" t="n">
-        <v>1005</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
+        <v>671</v>
+      </c>
+      <c r="X24" t="n">
+        <v>56.1</v>
+      </c>
       <c r="Y24" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="AA24" t="n">
-        <v>-152</v>
+        <v>97</v>
       </c>
       <c r="AB24" t="n">
-        <v>-6.5</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.24</v>
+        <v>11.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>16.21</v>
       </c>
       <c r="AG24" t="n">
-        <v>594.08</v>
+        <v>255.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>547.55</v>
+        <v>187.89</v>
       </c>
       <c r="AI24" t="n">
-        <v>29.2</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="n">
-        <v>593.6235208886742</v>
+        <v>238.0921052631579</v>
       </c>
       <c r="AK24" t="n">
-        <v>8.9</v>
+        <v>4.8</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>322003</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>2458195</v>
+        <v>18095000</v>
       </c>
       <c r="BC24" t="n">
-        <v>2458195</v>
+        <v>18095000</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6164,10 +6166,10 @@
         <v>0</v>
       </c>
       <c r="BO24" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
@@ -6179,12 +6181,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -6196,40 +6198,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>249.6</v>
+        <v>201.63</v>
       </c>
       <c r="J25" t="n">
-        <v>243.52</v>
+        <v>191.87</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="L25" t="n">
-        <v>67.65000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="N25" t="n">
-        <v>11080000</v>
+        <v>13430794</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>11080000</v>
+        <v>13430794</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -6247,105 +6249,105 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.165</v>
+        <v>0.038</v>
       </c>
       <c r="W25" t="n">
-        <v>671</v>
+        <v>3539</v>
       </c>
       <c r="X25" t="n">
-        <v>56.1</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>207.06</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>193.72</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>191.8684857142857</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>97</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>255.85</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>187.89</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>238.0921052631579</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -6354,13 +6356,13 @@
         <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BB25" t="n">
-        <v>18095000</v>
+        <v>13430794</v>
       </c>
       <c r="BC25" t="n">
-        <v>18095000</v>
+        <v>13430794</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
@@ -6396,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="BO25" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BP25" t="n">
         <v>2</v>
@@ -6411,12 +6413,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6428,40 +6430,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>230.91</v>
+        <v>646.6</v>
       </c>
       <c r="J26" t="n">
-        <v>234.4</v>
+        <v>593.62</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="L26" t="n">
-        <v>67.13</v>
+        <v>74.02</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6479,96 +6481,94 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.043</v>
+        <v>0.024</v>
       </c>
       <c r="W26" t="n">
-        <v>693</v>
-      </c>
-      <c r="X26" t="n">
-        <v>11.3</v>
-      </c>
+        <v>1005</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>-152</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.54</v>
+        <v>-6.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>14.8</v>
+        <v>9.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.11</v>
+        <v>2.23</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>227.44</v>
+        <v>594.08</v>
       </c>
       <c r="AH26" t="n">
-        <v>205</v>
+        <v>547.55</v>
       </c>
       <c r="AI26" t="n">
-        <v>37.8</v>
+        <v>29.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>234.4008293560754</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK26" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="AS26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AT26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
@@ -6580,19 +6580,19 @@
         <v>3</v>
       </c>
       <c r="AY26" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2995877</v>
+        <v>322003</v>
       </c>
       <c r="BA26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="BB26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="BC26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6625,19 +6625,19 @@
         <v>0</v>
       </c>
       <c r="BN26" t="n">
-        <v>2995877</v>
+        <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>2995877</v>
+        <v>2458195</v>
       </c>
       <c r="BP26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
       </c>
       <c r="BR26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -6875,12 +6875,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6892,40 +6892,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>165</v>
+        <v>147.51</v>
       </c>
       <c r="J28" t="n">
-        <v>83.06</v>
+        <v>171.84</v>
       </c>
       <c r="K28" t="n">
-        <v>98.7</v>
+        <v>-14.2</v>
       </c>
       <c r="L28" t="n">
-        <v>72.53</v>
+        <v>74.59</v>
       </c>
       <c r="M28" t="n">
-        <v>0.42</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4186225</v>
+        <v>10997624</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4186225</v>
+        <v>10997624</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -6939,94 +6939,94 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.037</v>
+        <v>0.059</v>
       </c>
       <c r="W28" t="n">
-        <v>1140</v>
+        <v>1871</v>
       </c>
       <c r="X28" t="n">
-        <v>122</v>
+        <v>42.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.43</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.710000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>3.67</v>
+        <v>23</v>
       </c>
       <c r="AG28" t="n">
-        <v>121.61</v>
+        <v>182.53</v>
       </c>
       <c r="AH28" t="n">
-        <v>75.76000000000001</v>
+        <v>499.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>229.7</v>
+        <v>19.9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>83.06001984126983</v>
+        <v>170.7900804020101</v>
       </c>
       <c r="AK28" t="n">
-        <v>98.7</v>
+        <v>-13.6</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR28" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="AS28" t="n">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -7035,13 +7035,13 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -7050,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>28919876</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>33987226</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>33987226</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>0</v>
+        <v>28919876</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7107,12 +7107,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7124,40 +7124,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I29" t="n">
-        <v>147.51</v>
+        <v>165</v>
       </c>
       <c r="J29" t="n">
-        <v>171.84</v>
+        <v>83.06</v>
       </c>
       <c r="K29" t="n">
-        <v>-14.2</v>
+        <v>98.7</v>
       </c>
       <c r="L29" t="n">
-        <v>74.59</v>
+        <v>72.53</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>0.42</v>
       </c>
       <c r="N29" t="n">
-        <v>10997624</v>
+        <v>4186225</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>10997624</v>
+        <v>4186225</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7171,94 +7171,94 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.059</v>
+        <v>0.037</v>
       </c>
       <c r="W29" t="n">
-        <v>1871</v>
+        <v>1140</v>
       </c>
       <c r="X29" t="n">
-        <v>42.9</v>
+        <v>122</v>
       </c>
       <c r="Y29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="n">
-        <v>17</v>
+        <v>1.43</v>
       </c>
       <c r="AA29" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.8</v>
+        <v>0.34</v>
       </c>
       <c r="AC29" t="n">
-        <v>30.3</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>3.67</v>
       </c>
       <c r="AG29" t="n">
-        <v>182.53</v>
+        <v>121.61</v>
       </c>
       <c r="AH29" t="n">
-        <v>499.2</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AI29" t="n">
-        <v>19.9</v>
+        <v>229.7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>170.7900804020101</v>
+        <v>83.06001984126983</v>
       </c>
       <c r="AK29" t="n">
-        <v>-13.6</v>
+        <v>98.7</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="AT29" t="n">
         <v>0</v>
@@ -7267,13 +7267,13 @@
         <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>28919876</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>33987226</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>33987226</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>28919876</v>
+        <v>0</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -9911,25 +9911,25 @@
         <v>26.36</v>
       </c>
       <c r="J41" t="n">
-        <v>32.21</v>
+        <v>31.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-18.2</v>
+        <v>-16.7</v>
       </c>
       <c r="L41" t="n">
         <v>61.81</v>
       </c>
       <c r="M41" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="N41" t="n">
-        <v>8341370</v>
+        <v>7567370</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>8341370</v>
+        <v>7567370</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -9943,7 +9943,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.299</v>
+        <v>0.271</v>
       </c>
       <c r="W41" t="n">
         <v>279</v>
@@ -9993,10 +9993,10 @@
         <v>5.1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>32.20606177606177</v>
+        <v>31.6626359832636</v>
       </c>
       <c r="AK41" t="n">
-        <v>-18.2</v>
+        <v>-16.7</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AQ41" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AR41" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AS41" t="n">
         <v>2</v>
@@ -11763,28 +11763,28 @@
         <v>806.1</v>
       </c>
       <c r="J49" t="n">
-        <v>241.63</v>
+        <v>243.4</v>
       </c>
       <c r="K49" t="n">
-        <v>233.6</v>
+        <v>231.2</v>
       </c>
       <c r="L49" t="n">
         <v>60.24</v>
       </c>
       <c r="M49" t="n">
-        <v>7.67</v>
+        <v>3.65</v>
       </c>
       <c r="N49" t="n">
-        <v>76695745</v>
+        <v>36537959</v>
       </c>
       <c r="O49" t="n">
-        <v>80376270</v>
+        <v>40279632</v>
       </c>
       <c r="P49" t="n">
-        <v>-3680525</v>
+        <v>-3741673</v>
       </c>
       <c r="Q49" t="n">
-        <v>104.8</v>
+        <v>110.24</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -11845,10 +11845,10 @@
         <v>285.8</v>
       </c>
       <c r="AJ49" t="n">
-        <v>241.6253276457393</v>
+        <v>243.3981654187428</v>
       </c>
       <c r="AK49" t="n">
-        <v>233.6</v>
+        <v>231.2</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>23-06-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
@@ -11876,10 +11876,10 @@
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AS49" t="n">
         <v>92</v>
@@ -13395,19 +13395,19 @@
         <v>625.85</v>
       </c>
       <c r="D14" t="n">
-        <v>630.67</v>
+        <v>632.66</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F14" t="n">
         <v>64.68000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="H14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13593,245 +13593,245 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>177.35</v>
+        <v>216.79</v>
       </c>
       <c r="D20" t="n">
-        <v>169.88</v>
+        <v>210</v>
       </c>
       <c r="E20" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="F20" t="n">
-        <v>61.48</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>336</v>
+        <v>177.35</v>
       </c>
       <c r="D21" t="n">
-        <v>335.41</v>
+        <v>169.88</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="F21" t="n">
-        <v>68.48</v>
+        <v>61.48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>216.79</v>
+        <v>336</v>
       </c>
       <c r="D22" t="n">
-        <v>210</v>
+        <v>335.41</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
       <c r="F22" t="n">
-        <v>67.04000000000001</v>
+        <v>68.48</v>
       </c>
       <c r="G22" t="n">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>201.63</v>
+        <v>230.91</v>
       </c>
       <c r="D23" t="n">
-        <v>191.87</v>
+        <v>234.4</v>
       </c>
       <c r="E23" t="n">
-        <v>5.1</v>
+        <v>-1.5</v>
       </c>
       <c r="F23" t="n">
-        <v>70.02</v>
+        <v>67.13</v>
       </c>
       <c r="G23" t="n">
-        <v>1.34</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>646.6</v>
+        <v>249.6</v>
       </c>
       <c r="D24" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="E24" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>249.6</v>
+        <v>201.63</v>
       </c>
       <c r="D25" t="n">
-        <v>243.52</v>
+        <v>191.87</v>
       </c>
       <c r="E25" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="F25" t="n">
-        <v>67.65000000000001</v>
+        <v>70.02</v>
       </c>
       <c r="G25" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>230.91</v>
+        <v>646.6</v>
       </c>
       <c r="D26" t="n">
-        <v>234.4</v>
+        <v>593.62</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5</v>
+        <v>8.9</v>
       </c>
       <c r="F26" t="n">
-        <v>67.13</v>
+        <v>74.02</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
@@ -13873,70 +13873,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>165</v>
+        <v>147.51</v>
       </c>
       <c r="D28" t="n">
-        <v>83.06</v>
+        <v>171.84</v>
       </c>
       <c r="E28" t="n">
-        <v>98.7</v>
+        <v>-14.2</v>
       </c>
       <c r="F28" t="n">
-        <v>72.53</v>
+        <v>74.59</v>
       </c>
       <c r="G28" t="n">
-        <v>0.42</v>
+        <v>1.1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>147.51</v>
+        <v>165</v>
       </c>
       <c r="D29" t="n">
-        <v>171.84</v>
+        <v>83.06</v>
       </c>
       <c r="E29" t="n">
-        <v>-14.2</v>
+        <v>98.7</v>
       </c>
       <c r="F29" t="n">
-        <v>74.59</v>
+        <v>72.53</v>
       </c>
       <c r="G29" t="n">
-        <v>1.1</v>
+        <v>0.42</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -14340,19 +14340,19 @@
         <v>26.36</v>
       </c>
       <c r="D41" t="n">
-        <v>32.21</v>
+        <v>31.66</v>
       </c>
       <c r="E41" t="n">
-        <v>-18.2</v>
+        <v>-16.7</v>
       </c>
       <c r="F41" t="n">
         <v>61.81</v>
       </c>
       <c r="G41" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -14620,19 +14620,19 @@
         <v>806.1</v>
       </c>
       <c r="D49" t="n">
-        <v>241.63</v>
+        <v>243.4</v>
       </c>
       <c r="E49" t="n">
-        <v>233.6</v>
+        <v>231.2</v>
       </c>
       <c r="F49" t="n">
         <v>60.24</v>
       </c>
       <c r="G49" t="n">
-        <v>7.67</v>
+        <v>3.65</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>

--- a/output/2026-09-25/enriched_analysis.xlsx
+++ b/output/2026-09-25/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.349</v>
+        <v>3.32</v>
       </c>
       <c r="W2" t="n">
-        <v>2867</v>
+        <v>2892</v>
       </c>
       <c r="X2" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1089,16 +1089,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1106,40 +1106,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>998.35</v>
+        <v>342.35</v>
       </c>
       <c r="J3" t="n">
-        <v>782.48</v>
+        <v>324.3</v>
       </c>
       <c r="K3" t="n">
-        <v>27.6</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
-        <v>61.71</v>
+        <v>63.24</v>
       </c>
       <c r="M3" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="N3" t="n">
-        <v>28765495</v>
+        <v>27352743</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>28765495</v>
+        <v>27352743</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -1161,50 +1161,52 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.931</v>
+        <v>0.844</v>
       </c>
       <c r="W3" t="n">
-        <v>309</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="X3" t="n">
+        <v>149</v>
+      </c>
       <c r="Y3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.91</v>
+        <v>2.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>-184</v>
+        <v>264</v>
       </c>
       <c r="AB3" t="n">
-        <v>31.98</v>
+        <v>2.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.26</v>
+        <v>2.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>57.93</v>
+        <v>6.06</v>
       </c>
       <c r="AG3" t="n">
-        <v>793.38</v>
+        <v>323.96</v>
       </c>
       <c r="AH3" t="n">
-        <v>781.97</v>
+        <v>282.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>764.770506385412</v>
+        <v>324.5110955607154</v>
       </c>
       <c r="AK3" t="n">
-        <v>30.5</v>
+        <v>5.5</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -1218,12 +1220,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1232,103 +1234,103 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AR3" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="AS3" t="n">
         <v>3</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>151389</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>9269255</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>15856731</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>22239300</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>30606913</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>151389</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>15856731</v>
+      </c>
+      <c r="BP3" t="n">
         <v>3</v>
       </c>
-      <c r="AW3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>7473906</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>7473906</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>12648592</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>36110169</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>36110169</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7473906</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>12648592</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>1</v>
-      </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.5909</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1336,40 +1338,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>70.56</v>
+        <v>998.35</v>
       </c>
       <c r="J4" t="n">
-        <v>74.22</v>
+        <v>782.48</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.9</v>
+        <v>27.6</v>
       </c>
       <c r="L4" t="n">
-        <v>72.56999999999999</v>
+        <v>61.71</v>
       </c>
       <c r="M4" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="N4" t="n">
-        <v>20066329</v>
+        <v>28765495</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>20066329</v>
+        <v>28765495</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1383,60 +1385,58 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>0.965</v>
+        <v>0.959</v>
       </c>
       <c r="W4" t="n">
-        <v>208</v>
-      </c>
-      <c r="X4" t="n">
-        <v>8.83</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.97</v>
+        <v>11.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>17</v>
+        <v>-184</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.73</v>
+        <v>31.98</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.6</v>
+        <v>-0.26</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.86</v>
+        <v>0.1</v>
       </c>
       <c r="AE4" t="b">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.140000000000001</v>
+        <v>57.93</v>
       </c>
       <c r="AG4" t="n">
-        <v>63.7</v>
+        <v>793.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>52.78</v>
+        <v>781.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>63.2</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>74.21830535305453</v>
+        <v>764.770506385412</v>
       </c>
       <c r="AK4" t="n">
-        <v>-4.9</v>
+        <v>30.5</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1460,47 +1460,47 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AR4" t="n">
         <v>39</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
         <v>3</v>
       </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>773602</v>
+        <v>7473906</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3010090</v>
+        <v>7473906</v>
       </c>
       <c r="BA4" t="n">
-        <v>12347178</v>
+        <v>12648592</v>
       </c>
       <c r="BB4" t="n">
-        <v>20066329</v>
+        <v>36110169</v>
       </c>
       <c r="BC4" t="n">
-        <v>20066329</v>
+        <v>36110169</v>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
@@ -1533,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>773602</v>
+        <v>7473906</v>
       </c>
       <c r="BO4" t="n">
-        <v>12347178</v>
+        <v>12648592</v>
       </c>
       <c r="BP4" t="n">
         <v>1</v>
@@ -1545,22 +1545,22 @@
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.5909</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
         <v>17</v>
@@ -1580,28 +1580,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>262.7</v>
+        <v>70.56</v>
       </c>
       <c r="J5" t="n">
-        <v>265.56</v>
+        <v>74.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1</v>
+        <v>-4.9</v>
       </c>
       <c r="L5" t="n">
-        <v>64.63</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>1.33</v>
+        <v>2.01</v>
       </c>
       <c r="N5" t="n">
-        <v>13278006</v>
+        <v>20066329</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>13278006</v>
+        <v>20066329</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1615,64 +1615,64 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.052</v>
+        <v>0.96</v>
       </c>
       <c r="W5" t="n">
-        <v>2571</v>
+        <v>209</v>
       </c>
       <c r="X5" t="n">
-        <v>8.84</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>249</v>
+        <v>27.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>301</v>
+        <v>17</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.27</v>
+        <v>2.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="b">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>250.99</v>
+        <v>63.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>175.52</v>
+        <v>52.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>98.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>265.56012</v>
+        <v>74.21830535305453</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1.1</v>
+        <v>-4.9</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1687,52 +1687,52 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ5" t="n">
+        <v>35</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
         <v>1</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
         <v>18</v>
       </c>
-      <c r="AS5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2</v>
-      </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>773602</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>3010090</v>
       </c>
       <c r="BA5" t="n">
-        <v>13278006</v>
+        <v>12347178</v>
       </c>
       <c r="BB5" t="n">
-        <v>13278006</v>
+        <v>20066329</v>
       </c>
       <c r="BC5" t="n">
-        <v>13278006</v>
+        <v>20066329</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>773602</v>
       </c>
       <c r="BO5" t="n">
-        <v>13278006</v>
+        <v>12347178</v>
       </c>
       <c r="BP5" t="n">
         <v>1</v>
@@ -1777,63 +1777,63 @@
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>0.06270000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>101.72</v>
+        <v>262.7</v>
       </c>
       <c r="J6" t="n">
-        <v>75.68000000000001</v>
+        <v>265.56</v>
       </c>
       <c r="K6" t="n">
-        <v>34.4</v>
+        <v>-1.1</v>
       </c>
       <c r="L6" t="n">
-        <v>74.84999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="M6" t="n">
-        <v>3.14</v>
+        <v>1.33</v>
       </c>
       <c r="N6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1851,56 +1851,56 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.118</v>
+        <v>0.052</v>
       </c>
       <c r="W6" t="n">
-        <v>2656</v>
+        <v>2547</v>
       </c>
       <c r="X6" t="n">
-        <v>23.3</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>-3</v>
+        <v>36</v>
       </c>
       <c r="Z6" t="n">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="AA6" t="n">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>18.27</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.69</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE6" t="b">
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>66.31999999999999</v>
+        <v>250.99</v>
       </c>
       <c r="AH6" t="n">
-        <v>47.42</v>
+        <v>175.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>224.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>75.6844038997483</v>
+        <v>265.56012</v>
       </c>
       <c r="AK6" t="n">
-        <v>34.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1914,27 +1914,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS6" t="n">
         <v>17</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>16</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="BB6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="BC6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="BO6" t="n">
-        <v>31393588</v>
+        <v>13278006</v>
       </c>
       <c r="BP6" t="n">
         <v>1</v>
@@ -2015,12 +2015,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2035,37 +2035,37 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>25</v>
       </c>
       <c r="H7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>342.35</v>
+        <v>605.75</v>
       </c>
       <c r="J7" t="n">
-        <v>314.78</v>
+        <v>510.94</v>
       </c>
       <c r="K7" t="n">
-        <v>8.800000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="L7" t="n">
-        <v>63.24</v>
+        <v>62.09</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="N7" t="n">
-        <v>18048688</v>
+        <v>30622049</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>18048688</v>
+        <v>30622049</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2079,64 +2079,64 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.552</v>
+        <v>0.297</v>
       </c>
       <c r="W7" t="n">
-        <v>327</v>
+        <v>1030</v>
       </c>
       <c r="X7" t="n">
-        <v>151</v>
+        <v>10.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>30</v>
       </c>
       <c r="AA7" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.55</v>
+        <v>14.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.07</v>
+        <v>14.4</v>
       </c>
       <c r="AD7" t="n">
         <v>0.01</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.06</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>323.96</v>
+        <v>504.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>282.08</v>
+        <v>489.54</v>
       </c>
       <c r="AI7" t="n">
-        <v>44</v>
+        <v>40.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>316.4840516408908</v>
+        <v>510.9380308010612</v>
       </c>
       <c r="AK7" t="n">
-        <v>8.199999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2146,57 +2146,57 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="AR7" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
         <v>16</v>
       </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9</v>
-      </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2634989</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>15230216</v>
       </c>
       <c r="BA7" t="n">
-        <v>6552676</v>
+        <v>30148841</v>
       </c>
       <c r="BB7" t="n">
-        <v>12935245</v>
+        <v>30622049</v>
       </c>
       <c r="BC7" t="n">
-        <v>21302858</v>
+        <v>30622049</v>
       </c>
       <c r="BD7" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>2634989</v>
       </c>
       <c r="BO7" t="n">
-        <v>6552676</v>
+        <v>30148841</v>
       </c>
       <c r="BP7" t="n">
         <v>2</v>
@@ -2241,18 +2241,18 @@
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>0.08740000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G8" t="n">
         <v>25</v>
@@ -2276,28 +2276,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>605.75</v>
+        <v>101.72</v>
       </c>
       <c r="J8" t="n">
-        <v>510.94</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>18.6</v>
+        <v>34.4</v>
       </c>
       <c r="L8" t="n">
-        <v>62.09</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>30622049</v>
+        <v>31393588</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>30622049</v>
+        <v>31393588</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2311,64 +2311,64 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.294</v>
+        <v>0.122</v>
       </c>
       <c r="W8" t="n">
-        <v>1040</v>
+        <v>2575</v>
       </c>
       <c r="X8" t="n">
-        <v>10.2</v>
+        <v>22.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.66</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.4</v>
+        <v>15.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01</v>
+        <v>1.69</v>
       </c>
       <c r="AE8" t="b">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>504.42</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="AH8" t="n">
-        <v>489.54</v>
+        <v>47.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>40.7</v>
+        <v>224.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>510.9380308010612</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AK8" t="n">
-        <v>18.6</v>
+        <v>34.4</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2378,102 +2378,102 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>31393588</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>31393588</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>31393588</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>31393588</v>
+      </c>
+      <c r="BP8" t="n">
         <v>1</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2634989</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15230216</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>30148841</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>30622049</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>30622049</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>2634989</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>30148841</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.08740000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="W9" t="n">
-        <v>2752</v>
+        <v>2717</v>
       </c>
       <c r="X9" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.052</v>
+        <v>0.048</v>
       </c>
       <c r="W10" t="n">
-        <v>1570</v>
+        <v>1713</v>
       </c>
       <c r="X10" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
@@ -3248,10 +3248,10 @@
         <v>0.045</v>
       </c>
       <c r="W12" t="n">
-        <v>15843</v>
+        <v>15880</v>
       </c>
       <c r="X12" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="Y12" t="n">
         <v>83</v>
@@ -3477,13 +3477,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>2.337</v>
+        <v>2.322</v>
       </c>
       <c r="W13" t="n">
-        <v>2549</v>
+        <v>2566</v>
       </c>
       <c r="X13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y13" t="n">
         <v>6</v>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.384</v>
+        <v>0.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1155</v>
+        <v>1138</v>
       </c>
       <c r="X14" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="Y14" t="n">
         <v>21</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.156</v>
+        <v>0.144</v>
       </c>
       <c r="W15" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="X15" t="n">
-        <v>29.7</v>
+        <v>32.3</v>
       </c>
       <c r="Y15" t="n">
         <v>19</v>
@@ -4101,16 +4101,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4118,40 +4118,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I16" t="n">
-        <v>388</v>
+        <v>191.59</v>
       </c>
       <c r="J16" t="n">
-        <v>338.1</v>
+        <v>170.45</v>
       </c>
       <c r="K16" t="n">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="L16" t="n">
-        <v>66.73</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>3381000</v>
+        <v>2560187</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3381000</v>
+        <v>2560187</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4165,69 +4165,69 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.074</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
-        <v>457</v>
+        <v>256</v>
       </c>
       <c r="X16" t="n">
-        <v>13.5</v>
+        <v>27.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>-8</v>
+        <v>24</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>33</v>
+        <v>-31</v>
       </c>
       <c r="AB16" t="n">
-        <v>14.36</v>
+        <v>3.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.94</v>
+        <v>4.96</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>2.97</v>
       </c>
       <c r="AG16" t="n">
-        <v>357.03</v>
+        <v>180.84</v>
       </c>
       <c r="AH16" t="n">
-        <v>269.34</v>
+        <v>163.56</v>
       </c>
       <c r="AI16" t="n">
-        <v>87.5</v>
+        <v>51.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>338.1</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK16" t="n">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -4237,22 +4237,22 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>5120374</v>
       </c>
       <c r="BB16" t="n">
-        <v>3381000</v>
+        <v>5120374</v>
       </c>
       <c r="BC16" t="n">
-        <v>3381000</v>
+        <v>5120374</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4318,10 +4318,10 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>5120374</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ16" t="n">
         <v>0</v>
@@ -4333,57 +4333,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>191.59</v>
+        <v>388</v>
       </c>
       <c r="J17" t="n">
-        <v>170.45</v>
+        <v>338.1</v>
       </c>
       <c r="K17" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="L17" t="n">
-        <v>67.54000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="M17" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="N17" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2560187</v>
+        <v>3381000</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4397,69 +4397,69 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.099</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>258</v>
+        <v>468</v>
       </c>
       <c r="X17" t="n">
-        <v>27.6</v>
+        <v>13.8</v>
       </c>
       <c r="Y17" t="n">
+        <v>-8</v>
+      </c>
+      <c r="Z17" t="n">
         <v>24</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AA17" t="n">
-        <v>-31</v>
+        <v>33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.36</v>
+        <v>14.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.96</v>
+        <v>9.94</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AE17" t="b">
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.97</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
-        <v>180.84</v>
+        <v>357.03</v>
       </c>
       <c r="AH17" t="n">
-        <v>163.56</v>
+        <v>269.34</v>
       </c>
       <c r="AI17" t="n">
-        <v>51.7</v>
+        <v>87.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>170.4518641810919</v>
+        <v>338.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -4469,22 +4469,22 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
@@ -4493,13 +4493,13 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>5120374</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>5120374</v>
+        <v>3381000</v>
       </c>
       <c r="BC17" t="n">
-        <v>5120374</v>
+        <v>3381000</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>5120374</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
         <v>0</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>2.835</v>
+        <v>2.873</v>
       </c>
       <c r="W18" t="n">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="X18" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="Y18" t="n">
         <v>30</v>
@@ -4791,16 +4791,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4808,229 +4808,231 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
+        <v>21</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>216.79</v>
+      </c>
+      <c r="J19" t="n">
+        <v>210.17</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67.04000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6039726</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6039726</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>13</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W19" t="n">
+        <v>195</v>
+      </c>
+      <c r="X19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>209.69</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>196.32</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>210.1724605908759</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>35</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV19" t="n">
         <v>9</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>64.48999999999999</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5656038</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5656038</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S19" t="b">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>9</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="W19" t="n">
-        <v>797</v>
-      </c>
-      <c r="X19" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>41</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AE19" t="b">
+      <c r="AW19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>94734</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1804945</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>3391225</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6039726</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6039726</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>94734</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3391225</v>
+      </c>
+      <c r="BP19" t="n">
         <v>1</v>
       </c>
-      <c r="AF19" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>66.43000000000001</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>64.33497045790251</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>39</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2601121</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2601121</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8710955</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>8710955</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>2601121</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>4</v>
-      </c>
       <c r="BQ19" t="n">
         <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5038,150 +5040,148 @@
         </is>
       </c>
       <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>64.29000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5656038</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5656038</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>811</v>
+      </c>
+      <c r="X20" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>41</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>64.33497045790251</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" t="n">
-        <v>21</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>216.79</v>
-      </c>
-      <c r="J20" t="n">
-        <v>210</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>67.04000000000001</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>5944992</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S20" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>12</v>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="W20" t="n">
-        <v>203</v>
-      </c>
-      <c r="X20" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>209.69</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>196.32</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>210.0036030944223</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8</v>
-      </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>12</v>
@@ -5193,16 +5193,16 @@
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1710211</v>
+        <v>2601121</v>
       </c>
       <c r="BA20" t="n">
-        <v>3296491</v>
+        <v>2601121</v>
       </c>
       <c r="BB20" t="n">
-        <v>5944992</v>
+        <v>8710955</v>
       </c>
       <c r="BC20" t="n">
-        <v>5944992</v>
+        <v>8710955</v>
       </c>
       <c r="BD20" t="n">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="BO20" t="n">
-        <v>3296491</v>
+        <v>2601121</v>
       </c>
       <c r="BP20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BQ20" t="n">
         <v>0</v>
@@ -5253,12 +5253,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5270,40 +5270,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G21" t="n">
         <v>13</v>
       </c>
       <c r="H21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>177.35</v>
+        <v>79.61</v>
       </c>
       <c r="J21" t="n">
-        <v>169.88</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="L21" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -5317,60 +5317,60 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.285</v>
+        <v>0.489</v>
       </c>
       <c r="W21" t="n">
-        <v>210</v>
+        <v>408</v>
       </c>
       <c r="X21" t="n">
-        <v>36.4</v>
+        <v>37.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>-44</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>-3.28</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>141</v>
+        <v>-19</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.05</v>
+        <v>1.54</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.25</v>
+        <v>8.73</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="AE21" t="b">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>-35.96</v>
+        <v>41.64</v>
       </c>
       <c r="AG21" t="n">
-        <v>175.12</v>
+        <v>77.63</v>
       </c>
       <c r="AH21" t="n">
-        <v>179.25</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AI21" t="n">
-        <v>24.8</v>
+        <v>7.7</v>
       </c>
       <c r="AJ21" t="n">
-        <v>169.8778156028369</v>
+        <v>81.10277768748172</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -5379,62 +5379,62 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AS21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT21" t="n">
         <v>1</v>
       </c>
       <c r="AU21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY21" t="n">
-        <v>2000469</v>
+        <v>1417187</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5988193</v>
+        <v>2802843</v>
       </c>
       <c r="BA21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="BB21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="BC21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
@@ -5467,10 +5467,10 @@
         <v>0</v>
       </c>
       <c r="BN21" t="n">
-        <v>2000469</v>
+        <v>1417187</v>
       </c>
       <c r="BO21" t="n">
-        <v>5988193</v>
+        <v>19959718</v>
       </c>
       <c r="BP21" t="n">
         <v>1</v>
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="BR21" t="n">
-        <v>0.3341</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -5557,13 +5557,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="W22" t="n">
-        <v>5507</v>
+        <v>5378</v>
       </c>
       <c r="X22" t="n">
-        <v>9.31</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y22" t="n">
         <v>43</v>
@@ -5717,16 +5717,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5734,40 +5734,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I23" t="n">
-        <v>230.91</v>
+        <v>177.35</v>
       </c>
       <c r="J23" t="n">
-        <v>234.4</v>
+        <v>169.88</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
-        <v>67.13</v>
+        <v>61.48</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5789,116 +5789,116 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.043</v>
+        <v>0.281</v>
       </c>
       <c r="W23" t="n">
-        <v>693</v>
+        <v>213</v>
       </c>
       <c r="X23" t="n">
-        <v>11.3</v>
+        <v>36.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>-5</v>
+        <v>-44</v>
       </c>
       <c r="Z23" t="n">
-        <v>32</v>
+        <v>-3.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.54</v>
+        <v>-4.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>14.8</v>
+        <v>8.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="AE23" t="b">
         <v>1</v>
       </c>
       <c r="AF23" t="n">
+        <v>-35.96</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>175.12</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>169.8778156028369</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>23-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR23" t="n">
         <v>9</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>227.44</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>205</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>234.4008293560754</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>21-09-2026</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>23-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4</v>
       </c>
       <c r="AS23" t="n">
         <v>2</v>
       </c>
       <c r="AT23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY23" t="n">
-        <v>2995877</v>
+        <v>2000469</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="BA23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="BB23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="BC23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
@@ -5931,10 +5931,10 @@
         <v>0</v>
       </c>
       <c r="BN23" t="n">
-        <v>2995877</v>
+        <v>2000469</v>
       </c>
       <c r="BO23" t="n">
-        <v>2995877</v>
+        <v>5988193</v>
       </c>
       <c r="BP23" t="n">
         <v>1</v>
@@ -5943,18 +5943,18 @@
         <v>0</v>
       </c>
       <c r="BR23" t="n">
-        <v>1</v>
+        <v>0.3341</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>17</v>
@@ -5978,28 +5978,28 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>249.6</v>
+        <v>230.91</v>
       </c>
       <c r="J24" t="n">
-        <v>243.52</v>
+        <v>234.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="L24" t="n">
-        <v>67.65000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>0.3</v>
       </c>
       <c r="N24" t="n">
-        <v>11080000</v>
+        <v>2995877</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>11080000</v>
+        <v>2995877</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -6017,120 +6017,120 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.165</v>
+        <v>0.043</v>
       </c>
       <c r="W24" t="n">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="X24" t="n">
-        <v>56.1</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.99</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>6.54</v>
       </c>
       <c r="AC24" t="n">
-        <v>11.6</v>
+        <v>14.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>16.21</v>
+        <v>9</v>
       </c>
       <c r="AG24" t="n">
-        <v>255.85</v>
+        <v>227.44</v>
       </c>
       <c r="AH24" t="n">
-        <v>187.89</v>
+        <v>205</v>
       </c>
       <c r="AI24" t="n">
-        <v>95</v>
+        <v>37.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>238.0921052631579</v>
+        <v>234.4008293560754</v>
       </c>
       <c r="AK24" t="n">
-        <v>4.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="AR24" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BB24" t="n">
-        <v>18095000</v>
+        <v>2995877</v>
       </c>
       <c r="BC24" t="n">
-        <v>18095000</v>
+        <v>2995877</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
@@ -6163,19 +6163,19 @@
         <v>0</v>
       </c>
       <c r="BN24" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BO24" t="n">
-        <v>0</v>
+        <v>2995877</v>
       </c>
       <c r="BP24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
       </c>
       <c r="BR24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -6253,13 +6253,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="W25" t="n">
-        <v>3539</v>
+        <v>3452</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="Y25" t="n">
         <v>-4</v>
@@ -6413,12 +6413,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -6430,40 +6430,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>646.6</v>
+        <v>249.6</v>
       </c>
       <c r="J26" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="K26" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="L26" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2458195</v>
+        <v>11080000</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -6481,118 +6481,120 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.024</v>
+        <v>0.158</v>
       </c>
       <c r="W26" t="n">
-        <v>1005</v>
-      </c>
-      <c r="X26" t="inlineStr"/>
+        <v>702</v>
+      </c>
+      <c r="X26" t="n">
+        <v>58.6</v>
+      </c>
       <c r="Y26" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="AA26" t="n">
-        <v>-152</v>
+        <v>97</v>
       </c>
       <c r="AB26" t="n">
-        <v>-6.5</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.24</v>
+        <v>11.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>16.21</v>
       </c>
       <c r="AG26" t="n">
-        <v>594.08</v>
+        <v>255.85</v>
       </c>
       <c r="AH26" t="n">
-        <v>547.55</v>
+        <v>187.89</v>
       </c>
       <c r="AI26" t="n">
-        <v>29.2</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>593.6235208886742</v>
+        <v>238.0921052631579</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.9</v>
+        <v>4.8</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AS26" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>322003</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>2458195</v>
+        <v>18095000</v>
       </c>
       <c r="BC26" t="n">
-        <v>2458195</v>
+        <v>18095000</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
@@ -6628,10 +6630,10 @@
         <v>0</v>
       </c>
       <c r="BO26" t="n">
-        <v>2458195</v>
+        <v>0</v>
       </c>
       <c r="BP26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BQ26" t="n">
         <v>0</v>
@@ -6643,16 +6645,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6660,40 +6662,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>79.61</v>
+        <v>646.6</v>
       </c>
       <c r="J27" t="n">
-        <v>81.11</v>
+        <v>593.62</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8</v>
+        <v>8.9</v>
       </c>
       <c r="L27" t="n">
-        <v>62.78</v>
+        <v>74.02</v>
       </c>
       <c r="M27" t="n">
-        <v>1.85</v>
+        <v>0.25</v>
       </c>
       <c r="N27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -6707,60 +6709,58 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.454</v>
+        <v>0.025</v>
       </c>
       <c r="W27" t="n">
-        <v>408</v>
-      </c>
-      <c r="X27" t="n">
-        <v>37.9</v>
-      </c>
+        <v>986</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>21</v>
+        <v>-2</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.390000000000001</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>-19</v>
+        <v>-152</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.54</v>
+        <v>-6.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.73</v>
+        <v>9.24</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.28</v>
+        <v>2.23</v>
       </c>
       <c r="AE27" t="b">
         <v>1</v>
       </c>
       <c r="AF27" t="n">
-        <v>41.64</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="n">
-        <v>77.63</v>
+        <v>594.08</v>
       </c>
       <c r="AH27" t="n">
-        <v>77.90000000000001</v>
+        <v>547.55</v>
       </c>
       <c r="AI27" t="n">
-        <v>7.7</v>
+        <v>29.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>81.11201466291054</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK27" t="n">
-        <v>-1.9</v>
+        <v>8.9</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
@@ -6784,17 +6784,17 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
         <v>28</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
@@ -6803,28 +6803,28 @@
         <v>1</v>
       </c>
       <c r="AV27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1385656</v>
+        <v>322003</v>
       </c>
       <c r="BA27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="BB27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="BC27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
@@ -6860,10 +6860,10 @@
         <v>0</v>
       </c>
       <c r="BO27" t="n">
-        <v>18542531</v>
+        <v>2458195</v>
       </c>
       <c r="BP27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ27" t="n">
         <v>0</v>
@@ -6875,12 +6875,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -6892,40 +6892,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>147.51</v>
+        <v>124.17</v>
       </c>
       <c r="J28" t="n">
-        <v>171.84</v>
+        <v>105.19</v>
       </c>
       <c r="K28" t="n">
-        <v>-14.2</v>
+        <v>18</v>
       </c>
       <c r="L28" t="n">
-        <v>74.59</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>2.63</v>
       </c>
       <c r="N28" t="n">
-        <v>10997624</v>
+        <v>26297500</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>10997624</v>
+        <v>26297500</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -6939,94 +6939,94 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="W28" t="n">
-        <v>1871</v>
+        <v>5116</v>
       </c>
       <c r="X28" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>-25</v>
       </c>
       <c r="Z28" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="AA28" t="n">
-        <v>83</v>
+        <v>-11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.8</v>
+        <v>1.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>30.3</v>
+        <v>10.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="AG28" t="n">
-        <v>182.53</v>
+        <v>112.98</v>
       </c>
       <c r="AH28" t="n">
-        <v>499.2</v>
+        <v>111.95</v>
       </c>
       <c r="AI28" t="n">
-        <v>19.9</v>
+        <v>36.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>170.7900804020101</v>
+        <v>105.19</v>
       </c>
       <c r="AK28" t="n">
-        <v>-13.6</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="AS28" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
@@ -7035,13 +7035,13 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -7050,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>28919876</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>33987226</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>33987226</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="BO28" t="n">
-        <v>28919876</v>
+        <v>0</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7182,10 +7182,10 @@
         <v>0.037</v>
       </c>
       <c r="W29" t="n">
-        <v>1140</v>
+        <v>1117</v>
       </c>
       <c r="X29" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Y29" t="n">
         <v>15</v>
@@ -7339,12 +7339,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -7356,40 +7356,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>124.17</v>
+        <v>147.51</v>
       </c>
       <c r="J30" t="n">
-        <v>105.19</v>
+        <v>171.84</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>-14.2</v>
       </c>
       <c r="L30" t="n">
-        <v>67.15000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="M30" t="n">
-        <v>2.63</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>26297500</v>
+        <v>10997624</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>26297500</v>
+        <v>10997624</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7403,94 +7403,94 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.052</v>
+        <v>0.059</v>
       </c>
       <c r="W30" t="n">
-        <v>5012</v>
+        <v>1857</v>
       </c>
       <c r="X30" t="n">
-        <v>32.7</v>
+        <v>42.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>-25</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="AA30" t="n">
-        <v>-11</v>
+        <v>83</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.48</v>
+        <v>0.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.7</v>
+        <v>30.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AE30" t="b">
         <v>1</v>
       </c>
       <c r="AF30" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>112.98</v>
+        <v>182.53</v>
       </c>
       <c r="AH30" t="n">
-        <v>111.95</v>
+        <v>499.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>36.3</v>
+        <v>19.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>105.19</v>
+        <v>170.7900804020101</v>
       </c>
       <c r="AK30" t="n">
-        <v>18</v>
+        <v>-13.6</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="AS30" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
@@ -7499,13 +7499,13 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -7514,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>28919876</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>33987226</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>33987226</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="BO30" t="n">
-        <v>0</v>
+        <v>28919876</v>
       </c>
       <c r="BP30" t="n">
         <v>1</v>
@@ -7649,7 +7649,7 @@
         <v>366</v>
       </c>
       <c r="X31" t="n">
-        <v>5.92</v>
+        <v>5.9</v>
       </c>
       <c r="Y31" t="n">
         <v>118</v>
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="W32" t="n">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="X32" t="n">
-        <v>7.1</v>
+        <v>6.73</v>
       </c>
       <c r="Y32" t="n">
         <v>31</v>
@@ -8562,10 +8562,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W35" t="n">
-        <v>52400</v>
+        <v>53106</v>
       </c>
       <c r="X35" t="n">
-        <v>44.4</v>
+        <v>45</v>
       </c>
       <c r="Y35" t="n">
         <v>5</v>
@@ -8719,230 +8719,230 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E36" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>161.92</v>
+      </c>
+      <c r="J36" t="n">
+        <v>185.61</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>23998951</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>23998951</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="W36" t="n">
+        <v>646</v>
+      </c>
+      <c r="X36" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>168.06</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>191</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>185.6067362722351</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>23-06-2026</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ36" t="n">
+        <v>71</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>94</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW36" t="n">
         <v>2</v>
       </c>
-      <c r="F36" t="n">
-        <v>17</v>
-      </c>
-      <c r="G36" t="n">
-        <v>25</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1782.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>789.9400000000001</v>
-      </c>
-      <c r="K36" t="n">
-        <v>125.6</v>
-      </c>
-      <c r="L36" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="M36" t="n">
-        <v>12.76</v>
-      </c>
-      <c r="N36" t="n">
-        <v>127606073</v>
-      </c>
-      <c r="O36" t="n">
-        <v>130033072</v>
-      </c>
-      <c r="P36" t="n">
-        <v>-2426999</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>101.9</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Net Selling</t>
-        </is>
-      </c>
-      <c r="S36" t="b">
+      <c r="AX36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3009963</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>8001009</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>13998476</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3009963</v>
+      </c>
+      <c r="BP36" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
-        <v>6</v>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>3718</v>
-      </c>
-      <c r="X36" t="n">
-        <v>83.7</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1633.06</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1385.6</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>789.9446136512771</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>125.6</v>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>92</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>92</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR36" t="n">
         <v>0</v>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="W37" t="n">
-        <v>9494</v>
+        <v>9531</v>
       </c>
       <c r="X37" t="n">
         <v>12.6</v>
@@ -9183,12 +9183,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -9200,213 +9200,213 @@
         </is>
       </c>
       <c r="E38" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" t="n">
+        <v>17</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1782.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>789.9400000000001</v>
+      </c>
+      <c r="K38" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="M38" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="N38" t="n">
+        <v>127606073</v>
+      </c>
+      <c r="O38" t="n">
+        <v>130033072</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-2426999</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Net Selling</t>
+        </is>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>6</v>
       </c>
-      <c r="F38" t="n">
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3692</v>
+      </c>
+      <c r="X38" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA38" t="n">
         <v>22</v>
       </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>161.92</v>
-      </c>
-      <c r="J38" t="n">
-        <v>185.61</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="L38" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="M38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>23998951</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>23998951</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="W38" t="n">
-        <v>654</v>
-      </c>
-      <c r="X38" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>45</v>
-      </c>
       <c r="AB38" t="n">
-        <v>3.1</v>
+        <v>5.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1633.06</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1385.6</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>789.9446136512771</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>92</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>92</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ38" t="n">
         <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>168.06</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>191</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>185.6067362722351</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>23-06-2026</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ38" t="n">
-        <v>71</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>94</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3009963</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>8001009</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>13998476</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO38" t="n">
-        <v>3009963</v>
-      </c>
-      <c r="BP38" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ38" t="n">
-        <v>0</v>
       </c>
       <c r="BR38" t="n">
         <v>0</v>
@@ -9487,13 +9487,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="W39" t="n">
-        <v>1528</v>
+        <v>1519</v>
       </c>
       <c r="X39" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y39" t="n">
         <v>6</v>
@@ -9722,10 +9722,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>493</v>
+        <v>517</v>
       </c>
       <c r="X40" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="Y40" t="n">
         <v>5</v>
@@ -9951,13 +9951,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.271</v>
+        <v>0.275</v>
       </c>
       <c r="W41" t="n">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="X41" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="Y41" t="n">
         <v>16</v>
@@ -10183,13 +10183,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.231</v>
+        <v>0.234</v>
       </c>
       <c r="W42" t="n">
-        <v>977</v>
+        <v>964</v>
       </c>
       <c r="X42" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="Y42" t="n">
         <v>9</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
       <c r="W43" t="n">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="X43" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="Y43" t="n">
         <v>61</v>
@@ -10648,10 +10648,10 @@
         <v>0.075</v>
       </c>
       <c r="W44" t="n">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="X44" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="Y44" t="n">
         <v>185</v>
@@ -10875,10 +10875,10 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.224</v>
+        <v>0.225</v>
       </c>
       <c r="W45" t="n">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="X45" t="n">
         <v>18.8</v>
@@ -11107,13 +11107,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.21</v>
+        <v>0.206</v>
       </c>
       <c r="W46" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="X46" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="Y46" t="n">
         <v>21</v>
@@ -11339,13 +11339,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="W47" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="X47" t="n">
-        <v>97.8</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="Y47" t="n">
         <v>246</v>
@@ -11363,7 +11363,7 @@
         <v>2.07</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
@@ -11574,10 +11574,10 @@
         <v>0.043</v>
       </c>
       <c r="W48" t="n">
-        <v>1622</v>
+        <v>1611</v>
       </c>
       <c r="X48" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -11806,10 +11806,10 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2819</v>
+        <v>2960</v>
       </c>
       <c r="X49" t="n">
-        <v>834</v>
+        <v>876</v>
       </c>
       <c r="Y49" t="n">
         <v>3</v>
@@ -12038,10 +12038,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>8901</v>
+        <v>8835</v>
       </c>
       <c r="X50" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
         <v>21</v>
@@ -12270,10 +12270,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>118106</v>
+        <v>117616</v>
       </c>
       <c r="X51" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="Y51" t="n">
         <v>18</v>
@@ -12499,13 +12499,13 @@
         </is>
       </c>
       <c r="V52" t="n">
-        <v>0.526</v>
+        <v>0.534</v>
       </c>
       <c r="W52" t="n">
-        <v>3679</v>
+        <v>3623</v>
       </c>
       <c r="X52" t="n">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="Y52" t="n">
         <v>2</v>
@@ -12734,10 +12734,10 @@
         <v>0.083</v>
       </c>
       <c r="W53" t="n">
-        <v>1655</v>
+        <v>1648</v>
       </c>
       <c r="X53" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="Y53" t="n">
         <v>39</v>
@@ -12998,31 +12998,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>NURECA LIMITED</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>998.35</v>
+        <v>342.35</v>
       </c>
       <c r="D3" t="n">
-        <v>782.48</v>
+        <v>324.3</v>
       </c>
       <c r="E3" t="n">
-        <v>27.6</v>
+        <v>5.6</v>
       </c>
       <c r="F3" t="n">
-        <v>61.71</v>
+        <v>63.24</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -13033,175 +13033,175 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.56</v>
+        <v>998.35</v>
       </c>
       <c r="D4" t="n">
-        <v>74.22</v>
+        <v>782.48</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.9</v>
+        <v>27.6</v>
       </c>
       <c r="F4" t="n">
-        <v>72.56999999999999</v>
+        <v>61.71</v>
       </c>
       <c r="G4" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GANDHAR</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>262.7</v>
+        <v>70.56</v>
       </c>
       <c r="D5" t="n">
-        <v>265.56</v>
+        <v>74.22</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1</v>
+        <v>-4.9</v>
       </c>
       <c r="F5" t="n">
-        <v>64.63</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1.33</v>
+        <v>2.01</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>101.72</v>
+        <v>262.7</v>
       </c>
       <c r="D6" t="n">
-        <v>75.68000000000001</v>
+        <v>265.56</v>
       </c>
       <c r="E6" t="n">
-        <v>34.4</v>
+        <v>-1.1</v>
       </c>
       <c r="F6" t="n">
-        <v>74.84999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="G6" t="n">
-        <v>3.14</v>
+        <v>1.33</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NURECA</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NURECA LIMITED</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342.35</v>
+        <v>605.75</v>
       </c>
       <c r="D7" t="n">
-        <v>314.78</v>
+        <v>510.94</v>
       </c>
       <c r="E7" t="n">
-        <v>8.800000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="F7" t="n">
-        <v>63.24</v>
+        <v>62.09</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>3.06</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>21-09-2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>605.75</v>
+        <v>101.72</v>
       </c>
       <c r="D8" t="n">
-        <v>510.94</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>18.6</v>
+        <v>34.4</v>
       </c>
       <c r="F8" t="n">
-        <v>62.09</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
@@ -13453,70 +13453,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>388</v>
+        <v>191.59</v>
       </c>
       <c r="D16" t="n">
-        <v>338.1</v>
+        <v>170.45</v>
       </c>
       <c r="E16" t="n">
-        <v>14.8</v>
+        <v>12.4</v>
       </c>
       <c r="F16" t="n">
-        <v>66.73</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>191.59</v>
+        <v>388</v>
       </c>
       <c r="D17" t="n">
-        <v>170.45</v>
+        <v>338.1</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4</v>
+        <v>14.8</v>
       </c>
       <c r="F17" t="n">
-        <v>67.54000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="G17" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
@@ -13558,105 +13558,105 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>TAINWALCHM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64.8</v>
+        <v>216.79</v>
       </c>
       <c r="D19" t="n">
-        <v>64.48999999999999</v>
+        <v>210.17</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="F19" t="n">
-        <v>64.29000000000001</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TAINWALCHM</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TAINWALA CHEMICALS AND PLASTICS (INDIA) LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>216.79</v>
+        <v>64.8</v>
       </c>
       <c r="D20" t="n">
-        <v>210</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>67.04000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>177.35</v>
+        <v>79.61</v>
       </c>
       <c r="D21" t="n">
-        <v>169.88</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4</v>
+        <v>-1.8</v>
       </c>
       <c r="F21" t="n">
-        <v>61.48</v>
+        <v>62.78</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
@@ -13698,31 +13698,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JAYAGROGN</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jayant Agro-Organics Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>230.91</v>
+        <v>177.35</v>
       </c>
       <c r="D23" t="n">
-        <v>234.4</v>
+        <v>169.88</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5</v>
+        <v>4.4</v>
       </c>
       <c r="F23" t="n">
-        <v>67.13</v>
+        <v>61.48</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13733,35 +13733,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>JAYAGROGN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Jayant Agro-Organics Limited</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>249.6</v>
+        <v>230.91</v>
       </c>
       <c r="D24" t="n">
-        <v>243.52</v>
+        <v>234.4</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>-1.5</v>
       </c>
       <c r="F24" t="n">
-        <v>67.65000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="G24" t="n">
-        <v>1.11</v>
+        <v>0.3</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
@@ -13803,105 +13803,105 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>646.6</v>
+        <v>249.6</v>
       </c>
       <c r="D26" t="n">
-        <v>593.62</v>
+        <v>243.52</v>
       </c>
       <c r="E26" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="F26" t="n">
-        <v>74.02</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>79.61</v>
+        <v>646.6</v>
       </c>
       <c r="D27" t="n">
-        <v>81.11</v>
+        <v>593.62</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8</v>
+        <v>8.9</v>
       </c>
       <c r="F27" t="n">
-        <v>62.78</v>
+        <v>74.02</v>
       </c>
       <c r="G27" t="n">
-        <v>1.85</v>
+        <v>0.25</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>MAN INFRACONSTRUCTION LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>147.51</v>
+        <v>124.17</v>
       </c>
       <c r="D28" t="n">
-        <v>171.84</v>
+        <v>105.19</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.2</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>74.59</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1</v>
+        <v>2.63</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -13943,35 +13943,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAN INFRACONSTRUCTION LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>124.17</v>
+        <v>147.51</v>
       </c>
       <c r="D30" t="n">
-        <v>105.19</v>
+        <v>171.84</v>
       </c>
       <c r="E30" t="n">
-        <v>18</v>
+        <v>-14.2</v>
       </c>
       <c r="F30" t="n">
-        <v>67.15000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="G30" t="n">
-        <v>2.63</v>
+        <v>1.1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
@@ -14153,35 +14153,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1782.3</v>
+        <v>161.92</v>
       </c>
       <c r="D36" t="n">
-        <v>789.9400000000001</v>
+        <v>185.61</v>
       </c>
       <c r="E36" t="n">
-        <v>125.6</v>
+        <v>-12.8</v>
       </c>
       <c r="F36" t="n">
-        <v>67.55</v>
+        <v>64.08</v>
       </c>
       <c r="G36" t="n">
-        <v>12.76</v>
+        <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
@@ -14223,35 +14223,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>161.92</v>
+        <v>1782.3</v>
       </c>
       <c r="D38" t="n">
-        <v>185.61</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-12.8</v>
+        <v>125.6</v>
       </c>
       <c r="F38" t="n">
-        <v>64.08</v>
+        <v>67.55</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4</v>
+        <v>12.76</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -14873,7 +14873,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
